--- a/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack.xlsx
+++ b/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C050083-C073-41A3-BEFA-516A84E57AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBC3510-29FE-493F-AD7D-7FE06AE0021D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="945" windowWidth="25575" windowHeight="13875" tabRatio="839" activeTab="2" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" activeTab="2" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="1" r:id="rId1"/>
@@ -193,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -233,7 +233,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -709,7 +708,7 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="6">
@@ -731,7 +730,7 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="20">
@@ -756,7 +755,7 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="11"/>
@@ -774,7 +773,6 @@
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="21"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
@@ -792,7 +790,7 @@
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="11"/>
@@ -891,7 +889,7 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="11"/>
@@ -1217,7 +1215,7 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="6">
@@ -1239,7 +1237,7 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="6">
@@ -1264,7 +1262,7 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="11"/>
@@ -1282,7 +1280,6 @@
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="21"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
@@ -1300,7 +1297,7 @@
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="11"/>
@@ -1399,7 +1396,7 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="11"/>
@@ -1725,7 +1722,7 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="6">
@@ -1747,7 +1744,7 @@
       <c r="D6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="6">
@@ -1772,7 +1769,7 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="11"/>
@@ -1790,7 +1787,6 @@
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="21"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
@@ -1808,7 +1804,7 @@
       <c r="D9" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="11"/>
@@ -1907,7 +1903,7 @@
       <c r="D10" t="s">
         <v>11</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" t="s">
         <v>23</v>
       </c>
       <c r="F10" s="11"/>

--- a/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack.xlsx
+++ b/Libraries/Vehicle/Steer/Rack/sm_car_data_Steer_Rack.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Steer\Rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBC3510-29FE-493F-AD7D-7FE06AE0021D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559887A5-0FE3-438C-B162-2726A704A34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="839" activeTab="2" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="6480" yWindow="810" windowWidth="21600" windowHeight="13230" tabRatio="839" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_HambaLG_f" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="30">
   <si>
     <t>Units</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>Must  be consistent with linkage trackrod inboard point</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>N/(m/s)</t>
   </si>
 </sst>
 </file>
@@ -237,7 +243,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="11">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -619,7 +639,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -767,201 +787,211 @@
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11">
-        <f>H13*$H$14</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I9" s="11">
-        <f t="shared" ref="I9:AB9" si="0">I13*$H$14</f>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J9" s="11">
-        <f t="shared" si="0"/>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K9" s="11">
-        <f t="shared" si="0"/>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L9" s="11">
-        <f t="shared" si="0"/>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M9" s="11">
-        <f t="shared" si="0"/>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N9" s="11">
-        <f t="shared" si="0"/>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O9" s="11">
-        <f t="shared" si="0"/>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P9" s="11">
-        <f t="shared" si="0"/>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q9" s="11">
-        <f t="shared" si="0"/>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R9" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="11">
-        <f t="shared" si="0"/>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T9" s="11">
-        <f t="shared" si="0"/>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U9" s="11">
-        <f t="shared" si="0"/>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V9" s="11">
-        <f t="shared" si="0"/>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W9" s="11">
-        <f t="shared" si="0"/>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X9" s="11">
-        <f t="shared" si="0"/>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y9" s="11">
-        <f t="shared" si="0"/>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z9" s="11">
-        <f t="shared" si="0"/>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA9" s="11">
-        <f t="shared" si="0"/>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB9" s="11">
-        <f t="shared" si="0"/>
-        <v>3.1415700000000002</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11">
+        <f>H14*$H$15</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I10" s="11">
+        <f t="shared" ref="I10:AB10" si="0">I14*$H$15</f>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J10" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K10" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L10" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M10" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N10" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O10" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P10" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q10" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R10" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V10" s="11">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W10" s="11">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X10" s="11">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y10" s="11">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z10" s="11">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA10" s="11">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB10" s="11">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11">
         <v>-0.3</v>
       </c>
-      <c r="I10">
+      <c r="I11">
         <v>-0.27300000000000002</v>
       </c>
-      <c r="J10">
+      <c r="J11">
         <v>-0.24360000000000001</v>
       </c>
-      <c r="K10">
+      <c r="K11">
         <v>-0.2112</v>
       </c>
-      <c r="L10">
+      <c r="L11">
         <v>-0.17780000000000001</v>
       </c>
-      <c r="M10">
+      <c r="M11">
         <v>-0.1462</v>
       </c>
-      <c r="N10">
+      <c r="N11">
         <v>-0.1178</v>
       </c>
-      <c r="O10">
+      <c r="O11">
         <v>-9.1200000000000003E-2</v>
       </c>
-      <c r="P10">
+      <c r="P11">
         <v>-6.3600000000000004E-2</v>
       </c>
-      <c r="Q10">
+      <c r="Q11">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="R10">
+      <c r="R11">
         <v>0</v>
       </c>
-      <c r="S10">
+      <c r="S11">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="T10">
+      <c r="T11">
         <v>6.3600000000000004E-2</v>
       </c>
-      <c r="U10">
+      <c r="U11">
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="V10">
+      <c r="V11">
         <v>0.1178</v>
       </c>
-      <c r="W10">
+      <c r="W11">
         <v>0.14630000000000001</v>
       </c>
-      <c r="X10">
+      <c r="X11">
         <v>0.17780000000000001</v>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <v>0.2112</v>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <v>0.24360000000000001</v>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <v>0.27300000000000002</v>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
@@ -971,80 +1001,80 @@
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="11">
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="11">
         <v>-180</v>
       </c>
-      <c r="I13">
+      <c r="I14">
         <v>-162</v>
       </c>
-      <c r="J13">
+      <c r="J14">
         <v>-144</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>-126</v>
       </c>
-      <c r="L13">
+      <c r="L14">
         <v>-108</v>
       </c>
-      <c r="M13">
+      <c r="M14">
         <v>-90</v>
       </c>
-      <c r="N13">
+      <c r="N14">
         <v>-72</v>
       </c>
-      <c r="O13">
+      <c r="O14">
         <v>-54</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>-36</v>
       </c>
-      <c r="Q13">
+      <c r="Q14">
         <v>-18</v>
       </c>
-      <c r="R13">
+      <c r="R14">
         <v>0</v>
       </c>
-      <c r="S13">
+      <c r="S14">
         <v>18</v>
       </c>
-      <c r="T13">
+      <c r="T14">
         <v>36</v>
       </c>
-      <c r="U13">
+      <c r="U14">
         <v>54</v>
       </c>
-      <c r="V13">
+      <c r="V14">
         <v>72</v>
       </c>
-      <c r="W13">
+      <c r="W14">
         <v>90</v>
       </c>
-      <c r="X13">
+      <c r="X14">
         <v>108</v>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <v>126</v>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <v>144</v>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <v>162</v>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="H14">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="H15">
         <f>3.14157/180</f>
         <v>1.7453166666666669E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
@@ -1072,7 +1102,6 @@
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="13"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -1084,6 +1113,7 @@
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="13"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -1094,26 +1124,41 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="13"/>
-      <c r="H25" s="14"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
       <c r="H26" s="14"/>
     </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
+      <c r="H27" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A25:A26">
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+  <conditionalFormatting sqref="A26:A27">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B10 A21:B24">
-    <cfRule type="cellIs" dxfId="7" priority="6" operator="equal">
+  <conditionalFormatting sqref="A4:B11">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E10">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+  <conditionalFormatting sqref="A22:B25">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"class"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E11">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1126,7 +1171,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -1274,201 +1319,211 @@
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11">
-        <f>H13*$H$14</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I9" s="11">
-        <f t="shared" ref="I9:AB9" si="0">I13*$H$14</f>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J9" s="11">
-        <f t="shared" si="0"/>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K9" s="11">
-        <f t="shared" si="0"/>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L9" s="11">
-        <f t="shared" si="0"/>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M9" s="11">
-        <f t="shared" si="0"/>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N9" s="11">
-        <f t="shared" si="0"/>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O9" s="11">
-        <f t="shared" si="0"/>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P9" s="11">
-        <f t="shared" si="0"/>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q9" s="11">
-        <f t="shared" si="0"/>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R9" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="11">
-        <f t="shared" si="0"/>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T9" s="11">
-        <f t="shared" si="0"/>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U9" s="11">
-        <f t="shared" si="0"/>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V9" s="11">
-        <f t="shared" si="0"/>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W9" s="11">
-        <f t="shared" si="0"/>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X9" s="11">
-        <f t="shared" si="0"/>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y9" s="11">
-        <f t="shared" si="0"/>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z9" s="11">
-        <f t="shared" si="0"/>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA9" s="11">
-        <f t="shared" si="0"/>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB9" s="11">
-        <f t="shared" si="0"/>
-        <v>3.1415700000000002</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11">
+        <f>H14*$H$15</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I10" s="11">
+        <f t="shared" ref="I10:AB10" si="0">I14*$H$15</f>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J10" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K10" s="11">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L10" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M10" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N10" s="11">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O10" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P10" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q10" s="11">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R10" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U10" s="11">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V10" s="11">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W10" s="11">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X10" s="11">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y10" s="11">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z10" s="11">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA10" s="11">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB10" s="11">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11">
         <v>-0.3</v>
       </c>
-      <c r="I10">
+      <c r="I11">
         <v>-0.27300000000000002</v>
       </c>
-      <c r="J10">
+      <c r="J11">
         <v>-0.24360000000000001</v>
       </c>
-      <c r="K10">
+      <c r="K11">
         <v>-0.2112</v>
       </c>
-      <c r="L10">
+      <c r="L11">
         <v>-0.17780000000000001</v>
       </c>
-      <c r="M10">
+      <c r="M11">
         <v>-0.1462</v>
       </c>
-      <c r="N10">
+      <c r="N11">
         <v>-0.1178</v>
       </c>
-      <c r="O10">
+      <c r="O11">
         <v>-9.1200000000000003E-2</v>
       </c>
-      <c r="P10">
+      <c r="P11">
         <v>-6.3600000000000004E-2</v>
       </c>
-      <c r="Q10">
+      <c r="Q11">
         <v>-3.3000000000000002E-2</v>
       </c>
-      <c r="R10">
+      <c r="R11">
         <v>0</v>
       </c>
-      <c r="S10">
+      <c r="S11">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="T10">
+      <c r="T11">
         <v>6.3600000000000004E-2</v>
       </c>
-      <c r="U10">
+      <c r="U11">
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="V10">
+      <c r="V11">
         <v>0.1178</v>
       </c>
-      <c r="W10">
+      <c r="W11">
         <v>0.14630000000000001</v>
       </c>
-      <c r="X10">
+      <c r="X11">
         <v>0.17780000000000001</v>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <v>0.2112</v>
       </c>
-      <c r="Z10">
+      <c r="Z11">
         <v>0.24360000000000001</v>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <v>0.27300000000000002</v>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
@@ -1478,80 +1533,80 @@
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="11">
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="11">
         <v>-180</v>
       </c>
-      <c r="I13">
+      <c r="I14">
         <v>-162</v>
       </c>
-      <c r="J13">
+      <c r="J14">
         <v>-144</v>
       </c>
-      <c r="K13">
+      <c r="K14">
         <v>-126</v>
       </c>
-      <c r="L13">
+      <c r="L14">
         <v>-108</v>
       </c>
-      <c r="M13">
+      <c r="M14">
         <v>-90</v>
       </c>
-      <c r="N13">
+      <c r="N14">
         <v>-72</v>
       </c>
-      <c r="O13">
+      <c r="O14">
         <v>-54</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>-36</v>
       </c>
-      <c r="Q13">
+      <c r="Q14">
         <v>-18</v>
       </c>
-      <c r="R13">
+      <c r="R14">
         <v>0</v>
       </c>
-      <c r="S13">
+      <c r="S14">
         <v>18</v>
       </c>
-      <c r="T13">
+      <c r="T14">
         <v>36</v>
       </c>
-      <c r="U13">
+      <c r="U14">
         <v>54</v>
       </c>
-      <c r="V13">
+      <c r="V14">
         <v>72</v>
       </c>
-      <c r="W13">
+      <c r="W14">
         <v>90</v>
       </c>
-      <c r="X13">
+      <c r="X14">
         <v>108</v>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <v>126</v>
       </c>
-      <c r="Z13">
+      <c r="Z14">
         <v>144</v>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <v>162</v>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="H14">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="H15">
         <f>3.14157/180</f>
         <v>1.7453166666666669E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
@@ -1579,7 +1634,6 @@
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="13"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -1591,6 +1645,7 @@
       <c r="H22" s="6"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="13"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -1601,25 +1656,30 @@
       <c r="H24" s="6"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="13"/>
-      <c r="H25" s="14"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
       <c r="H26" s="14"/>
     </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
+      <c r="H27" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A25:A26">
+  <conditionalFormatting sqref="A26:A27">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B10 A21:B24">
+  <conditionalFormatting sqref="A4:B11 A22:B25">
     <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E10">
+  <conditionalFormatting sqref="E5 E7:E11">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"class"</formula>
     </cfRule>
@@ -1633,7 +1693,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="13" customWidth="1"/>
@@ -1781,394 +1841,402 @@
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="A9" s="4"/>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="17">
-        <f t="shared" ref="H9:AB9" si="0">H14*$H$16</f>
-        <v>-3.1415700000000002</v>
-      </c>
-      <c r="I9" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.8274130000000004</v>
-      </c>
-      <c r="J9" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.5132560000000002</v>
-      </c>
-      <c r="K9" s="17">
-        <f t="shared" si="0"/>
-        <v>-2.1990990000000004</v>
-      </c>
-      <c r="L9" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.8849420000000003</v>
-      </c>
-      <c r="M9" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.5707850000000001</v>
-      </c>
-      <c r="N9" s="17">
-        <f t="shared" si="0"/>
-        <v>-1.2566280000000001</v>
-      </c>
-      <c r="O9" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.94247100000000017</v>
-      </c>
-      <c r="P9" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.62831400000000004</v>
-      </c>
-      <c r="Q9" s="17">
-        <f t="shared" si="0"/>
-        <v>-0.31415700000000002</v>
-      </c>
-      <c r="R9" s="18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S9" s="17">
-        <f t="shared" si="0"/>
-        <v>0.31415700000000002</v>
-      </c>
-      <c r="T9" s="17">
-        <f t="shared" si="0"/>
-        <v>0.62831400000000004</v>
-      </c>
-      <c r="U9" s="17">
-        <f t="shared" si="0"/>
-        <v>0.94247100000000017</v>
-      </c>
-      <c r="V9" s="17">
-        <f t="shared" si="0"/>
-        <v>1.2566280000000001</v>
-      </c>
-      <c r="W9" s="17">
-        <f t="shared" si="0"/>
-        <v>1.5707850000000001</v>
-      </c>
-      <c r="X9" s="17">
-        <f t="shared" si="0"/>
-        <v>1.8849420000000003</v>
-      </c>
-      <c r="Y9" s="17">
-        <f t="shared" si="0"/>
-        <v>2.1990990000000004</v>
-      </c>
-      <c r="Z9" s="17">
-        <f t="shared" si="0"/>
-        <v>2.5132560000000002</v>
-      </c>
-      <c r="AA9" s="17">
-        <f t="shared" si="0"/>
-        <v>2.8274130000000004</v>
-      </c>
-      <c r="AB9" s="17">
-        <f t="shared" si="0"/>
-        <v>3.1415700000000002</v>
+      <c r="H9" s="11">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="B10" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
-      <c r="H10" s="15">
-        <f t="shared" ref="H10:AB10" si="1">H12*$H$13</f>
+      <c r="H10" s="17">
+        <f t="shared" ref="H10:AB10" si="0">H15*$H$17</f>
+        <v>-3.1415700000000002</v>
+      </c>
+      <c r="I10" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.8274130000000004</v>
+      </c>
+      <c r="J10" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.5132560000000002</v>
+      </c>
+      <c r="K10" s="17">
+        <f t="shared" si="0"/>
+        <v>-2.1990990000000004</v>
+      </c>
+      <c r="L10" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.8849420000000003</v>
+      </c>
+      <c r="M10" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.5707850000000001</v>
+      </c>
+      <c r="N10" s="17">
+        <f t="shared" si="0"/>
+        <v>-1.2566280000000001</v>
+      </c>
+      <c r="O10" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.94247100000000017</v>
+      </c>
+      <c r="P10" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.62831400000000004</v>
+      </c>
+      <c r="Q10" s="17">
+        <f t="shared" si="0"/>
+        <v>-0.31415700000000002</v>
+      </c>
+      <c r="R10" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.31415700000000002</v>
+      </c>
+      <c r="T10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.62831400000000004</v>
+      </c>
+      <c r="U10" s="17">
+        <f t="shared" si="0"/>
+        <v>0.94247100000000017</v>
+      </c>
+      <c r="V10" s="17">
+        <f t="shared" si="0"/>
+        <v>1.2566280000000001</v>
+      </c>
+      <c r="W10" s="17">
+        <f t="shared" si="0"/>
+        <v>1.5707850000000001</v>
+      </c>
+      <c r="X10" s="17">
+        <f t="shared" si="0"/>
+        <v>1.8849420000000003</v>
+      </c>
+      <c r="Y10" s="17">
+        <f t="shared" si="0"/>
+        <v>2.1990990000000004</v>
+      </c>
+      <c r="Z10" s="17">
+        <f t="shared" si="0"/>
+        <v>2.5132560000000002</v>
+      </c>
+      <c r="AA10" s="17">
+        <f t="shared" si="0"/>
+        <v>2.8274130000000004</v>
+      </c>
+      <c r="AB10" s="17">
+        <f t="shared" si="0"/>
+        <v>3.1415700000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="15">
+        <f t="shared" ref="H11:AB11" si="1">H13*$H$14</f>
         <v>-0.18</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I11" s="15">
         <f t="shared" si="1"/>
         <v>-0.1638</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
         <v>-0.14616000000000001</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K11" s="15">
         <f t="shared" si="1"/>
         <v>-0.12672</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L11" s="15">
         <f t="shared" si="1"/>
         <v>-0.10668000000000001</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M11" s="15">
         <f t="shared" si="1"/>
         <v>-8.7719999999999992E-2</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N11" s="15">
         <f t="shared" si="1"/>
         <v>-7.0679999999999993E-2</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O11" s="15">
         <f t="shared" si="1"/>
         <v>-5.4719999999999998E-2</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P11" s="15">
         <f t="shared" si="1"/>
         <v>-3.8159999999999999E-2</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q11" s="15">
         <f t="shared" si="1"/>
         <v>-1.9800000000000002E-2</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R11" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S10" s="15">
+      <c r="S11" s="15">
         <f t="shared" si="1"/>
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="T10" s="15">
+      <c r="T11" s="15">
         <f t="shared" si="1"/>
         <v>3.8159999999999999E-2</v>
       </c>
-      <c r="U10" s="15">
+      <c r="U11" s="15">
         <f t="shared" si="1"/>
         <v>5.4719999999999998E-2</v>
       </c>
-      <c r="V10" s="15">
+      <c r="V11" s="15">
         <f t="shared" si="1"/>
         <v>7.0679999999999993E-2</v>
       </c>
-      <c r="W10" s="15">
+      <c r="W11" s="15">
         <f t="shared" si="1"/>
         <v>8.7780000000000011E-2</v>
       </c>
-      <c r="X10" s="15">
+      <c r="X11" s="15">
         <f t="shared" si="1"/>
         <v>0.10668000000000001</v>
       </c>
-      <c r="Y10" s="15">
+      <c r="Y11" s="15">
         <f t="shared" si="1"/>
         <v>0.12672</v>
       </c>
-      <c r="Z10" s="15">
+      <c r="Z11" s="15">
         <f t="shared" si="1"/>
         <v>0.14616000000000001</v>
       </c>
-      <c r="AA10" s="15">
+      <c r="AA11" s="15">
         <f t="shared" si="1"/>
         <v>0.1638</v>
       </c>
-      <c r="AB10" s="15">
+      <c r="AB11" s="15">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="11">
-        <v>-0.3</v>
-      </c>
-      <c r="I12">
-        <v>-0.27300000000000002</v>
-      </c>
-      <c r="J12">
-        <v>-0.24360000000000001</v>
-      </c>
-      <c r="K12">
-        <v>-0.2112</v>
-      </c>
-      <c r="L12">
-        <v>-0.17780000000000001</v>
-      </c>
-      <c r="M12">
-        <v>-0.1462</v>
-      </c>
-      <c r="N12">
-        <v>-0.1178</v>
-      </c>
-      <c r="O12">
-        <v>-9.1200000000000003E-2</v>
-      </c>
-      <c r="P12">
-        <v>-6.3600000000000004E-2</v>
-      </c>
-      <c r="Q12">
-        <v>-3.3000000000000002E-2</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T12">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="U12">
-        <v>9.1200000000000003E-2</v>
-      </c>
-      <c r="V12">
-        <v>0.1178</v>
-      </c>
-      <c r="W12">
-        <v>0.14630000000000001</v>
-      </c>
-      <c r="X12">
-        <v>0.17780000000000001</v>
-      </c>
-      <c r="Y12">
-        <v>0.2112</v>
-      </c>
-      <c r="Z12">
-        <v>0.24360000000000001</v>
-      </c>
-      <c r="AA12">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="AB12">
-        <v>0.3</v>
-      </c>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13">
+      <c r="H13" s="11">
+        <v>-0.3</v>
+      </c>
+      <c r="I13">
+        <v>-0.27300000000000002</v>
+      </c>
+      <c r="J13">
+        <v>-0.24360000000000001</v>
+      </c>
+      <c r="K13">
+        <v>-0.2112</v>
+      </c>
+      <c r="L13">
+        <v>-0.17780000000000001</v>
+      </c>
+      <c r="M13">
+        <v>-0.1462</v>
+      </c>
+      <c r="N13">
+        <v>-0.1178</v>
+      </c>
+      <c r="O13">
+        <v>-9.1200000000000003E-2</v>
+      </c>
+      <c r="P13">
+        <v>-6.3600000000000004E-2</v>
+      </c>
+      <c r="Q13">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T13">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="U13">
+        <v>9.1200000000000003E-2</v>
+      </c>
+      <c r="V13">
+        <v>0.1178</v>
+      </c>
+      <c r="W13">
+        <v>0.14630000000000001</v>
+      </c>
+      <c r="X13">
+        <v>0.17780000000000001</v>
+      </c>
+      <c r="Y13">
+        <v>0.2112</v>
+      </c>
+      <c r="Z13">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="AA13">
+        <v>0.27300000000000002</v>
+      </c>
+      <c r="AB13">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14">
         <f>0.6</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="H14" s="11">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="H15" s="11">
         <v>-180</v>
       </c>
-      <c r="I14">
+      <c r="I15">
         <v>-162</v>
       </c>
-      <c r="J14">
+      <c r="J15">
         <v>-144</v>
       </c>
-      <c r="K14">
+      <c r="K15">
         <v>-126</v>
       </c>
-      <c r="L14">
+      <c r="L15">
         <v>-108</v>
       </c>
-      <c r="M14">
+      <c r="M15">
         <v>-90</v>
       </c>
-      <c r="N14">
+      <c r="N15">
         <v>-72</v>
       </c>
-      <c r="O14">
+      <c r="O15">
         <v>-54</v>
       </c>
-      <c r="P14">
+      <c r="P15">
         <v>-36</v>
       </c>
-      <c r="Q14">
+      <c r="Q15">
         <v>-18</v>
       </c>
-      <c r="R14">
+      <c r="R15">
         <v>0</v>
       </c>
-      <c r="S14">
+      <c r="S15">
         <v>18</v>
       </c>
-      <c r="T14">
+      <c r="T15">
         <v>36</v>
       </c>
-      <c r="U14">
+      <c r="U15">
         <v>54</v>
       </c>
-      <c r="V14">
+      <c r="V15">
         <v>72</v>
       </c>
-      <c r="W14">
+      <c r="W15">
         <v>90</v>
       </c>
-      <c r="X14">
+      <c r="X15">
         <v>108</v>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <v>126</v>
       </c>
-      <c r="Z14">
+      <c r="Z15">
         <v>144</v>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <v>162</v>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <v>180</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
-      <c r="H16">
-        <f>3.14157/180</f>
-        <v>1.7453166666666669E-2</v>
-      </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="H17">
+        <f>3.14157/180</f>
+        <v>1.7453166666666669E-2</v>
+      </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
+      <c r="H18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="K19" s="19"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
     </row>
@@ -2176,12 +2244,10 @@
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="13"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -2194,43 +2260,52 @@
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" s="13"/>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B25" s="13"/>
-      <c r="H25" s="14"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
       <c r="H26" s="14"/>
     </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B27" s="13"/>
+      <c r="H27" s="14"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A25:A26">
+  <conditionalFormatting sqref="A26:A27">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:B10 A21:B24">
+  <conditionalFormatting sqref="A4:B11 A22:B25">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"class"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5 E7:E10">
+  <conditionalFormatting sqref="E5 E7:E11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"class"</formula>
     </cfRule>
